--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-18.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-18.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,37 +796,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FINLAND 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AC Oulu x FC Inter Turku</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AC Oulu</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>FC Inter Turku</t>
-        </is>
-      </c>
+          <t>Hapoel Tel Aviv x Hapoel Petah Tikva</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -819,37 +827,45 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="L5" t="n">
-        <v>4.17</v>
+        <v>9.09</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -864,32 +880,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>FINLAND 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MFK Karvina x H Slavia Kromeriz</t>
+          <t>AC Oulu x FC Inter Turku</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MFK Karvina</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>H Slavia Kromeriz</t>
+          <t>FC Inter Turku</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +914,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.24</v>
+        <v>4.17</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +945,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,37 +956,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GERMANY 2</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wolfsburg x SV Darmstadt</t>
+          <t>MFK Karvina x H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>MFK Karvina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SV Darmstadt</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +995,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="L7" t="n">
-        <v>5.88</v>
+        <v>17.24</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1026,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1037,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>GERMANY 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Slavia Sofia x CSKA 1948 Sofia</t>
+          <t>Wolfsburg x SV Darmstadt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>SV Darmstadt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1076,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4.76</v>
+        <v>5.88</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1087,6 +1107,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1101,32 +1123,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CYPRUS 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Omonia 29th May x AEK Larnaca</t>
+          <t>Slavia Sofia x CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia 29th May</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,13 +1157,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.16</v>
+        <v>4.76</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1166,6 +1188,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1199,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AUSTRIA 1</t>
+          <t>CYPRUS 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rapid Vienna x WSG Wattens</t>
+          <t>Omonia 29th May x AEK Larnaca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rapid Vienna</t>
+          <t>Omonia 29th May</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1238,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>20.41</v>
+        <v>13.16</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1269,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1280,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>AUSTRIA 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reims x Montpellier</t>
+          <t>Rapid Vienna x WSG Wattens</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rapid Vienna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1319,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>5.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L11" t="n">
-        <v>6.25</v>
+        <v>20.41</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1350,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,27 +1361,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Juve Stabia x Cesena</t>
+          <t>Reims x Montpellier</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1372,13 +1400,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -1403,6 +1431,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1442,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WALES 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ammanford AFC x Penybont FC</t>
+          <t>Juve Stabia x Cesena</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ammanford AFC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1481,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>13.51</v>
+        <v>6.45</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x5</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1482,6 +1512,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,27 +1523,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>WALES 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alianza Lima x Asociacion Deportiva Tarma</t>
+          <t>Ammanford AFC x Penybont FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Ammanford AFC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asociacion Deportiva Tarma</t>
+          <t>Penybont FC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1530,20 +1562,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="n">
-        <v>18.52</v>
+        <v>13.51</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1561,6 +1593,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1570,29 +1604,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv x Hapoel Petah Tikva</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>Boyaca Patriotas x Union Magdalena</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Union Magdalena</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1601,43 +1643,126 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>9.09</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
+        <v>200</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PERU 1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Alianza Lima x Asociacion Deportiva Tarma</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asociacion Deportiva Tarma</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="M16" t="n">
         <v>100</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3x0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-18.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-18.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1656,19 +1656,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1743,19 +1743,19 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
